--- a/data/mapping/phase1_hop2_stage_to_il.xlsx
+++ b/data/mapping/phase1_hop2_stage_to_il.xlsx
@@ -1916,7 +1916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1988,12 +1988,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>dim_customer_address_migration</t>
+          <t>dim_customer_migration</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>dim_address_rows</t>
+          <t>dim_customer_by_type</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2002,10 +2002,14 @@
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>customer_type_cd</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>dim_address_rows</t>
+          <t>dim_customer_by_type</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -2017,12 +2021,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>dim_reference_migration</t>
+          <t>dim_customer_address_migration</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>dim_ref_rows</t>
+          <t>dim_address_rows</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2034,10 +2038,39 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
+          <t>dim_address_rows</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>dim_reference_migration</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>dim_ref_rows</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>dim_ref_rows</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>

--- a/data/mapping/phase1_hop2_stage_to_il.xlsx
+++ b/data/mapping/phase1_hop2_stage_to_il.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -494,6 +494,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t xml:space="preserve">    per spec — nullable target columns carry it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - DIM_REFERENCE also lands ATTRIBUTE_MAP_CD — the NAICS lookup key</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    used by hop-3 CUSTOMER_CATEGORY.</t>
         </is>
       </c>
     </row>
@@ -706,7 +720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1900,6 +1914,50 @@
         </is>
       </c>
       <c r="J26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>dim_reference_migration</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>attribute_map_cd</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>attribute_map_cd</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
         <is>
           <t>yes</t>
         </is>

--- a/data/mapping/phase1_hop2_stage_to_il.xlsx
+++ b/data/mapping/phase1_hop2_stage_to_il.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Controls" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relations" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mapping" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rules" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -522,7 +523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -576,6 +577,11 @@
           <t>Enabled</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Requirement ID</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -620,6 +626,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>REQ-DA-201</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -664,6 +675,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>REQ-DA-202</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -706,6 +722,11 @@
       <c r="J4" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>REQ-DA-203</t>
         </is>
       </c>
     </row>
@@ -720,7 +741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -774,6 +795,16 @@
           <t>Enabled</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Business Rule</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Requirement ID</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -820,6 +851,16 @@
       <c r="J2" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>party key = 'CBS' + 'CUST' + bank number + customer number</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>REQ-DA-205</t>
         </is>
       </c>
     </row>
@@ -862,6 +903,12 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>direct copy</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -908,6 +955,16 @@
       <c r="J4" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>recode customer type 'N' to 'C'; otherwise keep the trimmed code</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>REQ-DA-206</t>
         </is>
       </c>
     </row>
@@ -954,6 +1011,12 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>direct copy</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1002,6 +1065,16 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>bank number, zero-padded to 3 digits</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>REQ-DA-207</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1050,6 +1123,16 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>constant 'CBS' — every row carries the CBS application key</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>REQ-DA-208</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1098,6 +1181,16 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>NAICS industry code, zero-padded to 6 digits</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>REQ-DA-209</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1146,6 +1239,16 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>customer name, whitespace trimmed</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>REQ-DA-210</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1194,6 +1297,16 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>first name kept for persons ('P') only; NULL otherwise</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>REQ-DA-211</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1242,6 +1355,16 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>tax id, zero-padded to 9 digits</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>REQ-DA-212</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1288,6 +1411,16 @@
       <c r="J12" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blank tax-id type defaults to 'S' (SSN)</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>REQ-DA-213</t>
         </is>
       </c>
     </row>
@@ -1334,6 +1467,16 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>birth date reformatted from YYYYMMDD to YYYY-MM-DD</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>REQ-DA-214</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1380,6 +1523,16 @@
       <c r="J14" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>last name kept for persons ('P') only; NULL otherwise</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>REQ-DA-211</t>
         </is>
       </c>
     </row>
@@ -1426,6 +1579,16 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>tax-id-type description carried from the join view (DIM_REFERENCE decode)</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>REQ-DA-215</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1474,6 +1637,16 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>party key = 'CBS' + 'CUST' + bank number + customer number</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>REQ-DA-205</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1522,6 +1695,16 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>country code, zero-padded to 5 digits</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>REQ-DA-216</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1570,6 +1753,16 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>address line 1, whitespace trimmed</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>REQ-DA-217</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1616,6 +1809,16 @@
       <c r="J19" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>address line 2, whitespace trimmed</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>REQ-DA-218</t>
         </is>
       </c>
     </row>
@@ -1662,6 +1865,12 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>direct copy</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1706,6 +1915,12 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>direct copy</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1750,6 +1965,12 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>direct copy</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1790,6 +2011,12 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>direct copy</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1834,6 +2061,12 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>direct copy</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1878,6 +2111,12 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>direct copy</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1918,6 +2157,12 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>direct copy</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1962,6 +2207,12 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>direct copy</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1974,7 +2225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2013,6 +2264,11 @@
           <t>Enabled</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Requirement ID</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2042,6 +2298,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>REQ-DC-201</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2073,6 +2334,11 @@
       <c r="G3" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>REQ-DA-204</t>
         </is>
       </c>
     </row>
@@ -2104,6 +2370,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>REQ-DC-202</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2131,6 +2402,11 @@
       <c r="G5" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>REQ-DC-203</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2174,6 +2450,11 @@
           <t>Enabled</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Requirement ID</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2199,6 +2480,11 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>REQ-DI-201</t>
         </is>
       </c>
     </row>
@@ -2236,4 +2522,151 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Test ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Rule Type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Source Table</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Source Column(s)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Target Table</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Target Column</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Transformation Logic</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Expected</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Where Clause</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Key Column</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Enabled</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Business Rule</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Requirement ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>BR-BIRTHDT-ISO</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>DATE_FORMAT</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>dim_customer</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>birth_dt</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>%Y-%m-%d</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>involved_party_key</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>birth date must be ISO YYYY-MM-DD after the hop-2 reformat</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>REQ-DI-202</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/mapping/phase1_hop2_stage_to_il.xlsx
+++ b/data/mapping/phase1_hop2_stage_to_il.xlsx
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -576,6 +576,11 @@
           <t>Enabled</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Source Tables</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -620,6 +625,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>cup00301, cup01201, dim_reference</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -664,6 +674,7 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -708,6 +719,7 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -720,7 +732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -774,6 +786,11 @@
           <t>Enabled</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -820,6 +837,11 @@
       <c r="J2" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Customer key built as 'CBSCUST' + bank code + customer number</t>
         </is>
       </c>
     </row>
@@ -862,6 +884,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Extract load date - copied unchanged</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -908,6 +935,11 @@
       <c r="J4" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Person flag: 'N' becomes 'C' (commercial); other values pass through</t>
         </is>
       </c>
     </row>
@@ -954,6 +986,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Legal entity code - copied unchanged</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1002,6 +1039,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Bank code left-padded to 3 digits</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1050,6 +1092,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Always 'CBS' - the source system identifier</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1098,6 +1145,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Industry code left-padded to 6 digits</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1146,6 +1198,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Customer name trimmed - becomes the full name</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1194,6 +1251,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>First name kept only for persons (P); organizations stay empty</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1242,6 +1304,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Tax id left-padded to 9 digits</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1288,6 +1355,11 @@
       <c r="J12" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Empty tax-id type defaults to 'S' (Social Security)</t>
         </is>
       </c>
     </row>
@@ -1334,6 +1406,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Birth date converted from YYYYMMDD to YYYY-MM-DD</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1380,6 +1457,11 @@
       <c r="J14" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Last name kept only for persons (P); organizations stay empty</t>
         </is>
       </c>
     </row>
@@ -1426,6 +1508,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Tax-id type description from the reference lookup</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1474,6 +1561,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Customer key built as 'CBSCUST' + bank code + customer number</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1522,6 +1614,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Country code left-padded to 5 digits</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1570,6 +1667,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Address line 1, trimmed</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1616,6 +1718,11 @@
       <c r="J19" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Address line 2, trimmed</t>
         </is>
       </c>
     </row>
@@ -1662,6 +1769,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>City - copied unchanged</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1706,6 +1818,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>State code - copied unchanged</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1748,6 +1865,11 @@
       <c r="J22" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Postal code - copied unchanged</t>
         </is>
       </c>
     </row>
@@ -1790,6 +1912,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Extract load date - copied unchanged</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1834,6 +1961,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Reference attribute code - copied unchanged</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1876,6 +2008,11 @@
       <c r="J25" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Reference value description - copied unchanged</t>
         </is>
       </c>
     </row>
@@ -1918,6 +2055,11 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Extract load date - copied unchanged</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1960,6 +2102,11 @@
       <c r="J27" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Category lookup key - copied unchanged</t>
         </is>
       </c>
     </row>
